--- a/detail/detail.xlsx
+++ b/detail/detail.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectSkripsi\trainModel\websites\detail\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectSkripsi\Skripsi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87775DA0-8409-42C9-A3A0-424E0A0C4D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1410B809-0F73-4418-9863-37497AB691F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D421E984-B7D9-42C2-B457-45490D1096D1}"/>
   </bookViews>
@@ -66,9 +66,6 @@
     <t>Topeng Bujuh</t>
   </si>
   <si>
-    <t>Tupeng Bondres</t>
-  </si>
-  <si>
     <t>## Ciri-Ciri Topeng
 Topeng Penasar menggambarkan sosok rakyat jelata atau abdi kerajaan dengan karakter yang komunikatif dan ekspresif. Tokohnya terbagi menjadi Penasar Kelihan yang berwibawa dan bersuara agung, serta Penasar Wijil yang lebih jenaka dan ekspresif dalam menunjukkan emosi seperti sedih, takut, maupun lucu.
 ## Peran
@@ -319,6 +316,9 @@
 Tokoh Sidakarya dipandang sebagai simbol turunnya Dewa Wisnu untuk menyelesaikan upacara dan mendatangkan kemakmuran bagi rakyat.
 # Penetralisir dan Pemberi Berkah
 Pada penghujung tariannya, penari menyebarkan Sekarura (beras kuning, irisan pandan, bunga, dan uang kepeng) ke segala arah mata angin dan kepada umat. Hal ini berperan sentral sebagai simbol kedermawanan, kesejahteraan, sekaligus menetralisir segala penyakit (klesa) baik dalam diri manusia (Bhuwana Alit) maupun di alam semesta (Bhuwana Agung).</t>
+  </si>
+  <si>
+    <t>Topeng Bondres</t>
   </si>
 </sst>
 </file>
@@ -693,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -701,13 +701,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -715,13 +715,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -729,13 +729,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="360" x14ac:dyDescent="0.3">
@@ -743,13 +743,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -757,13 +757,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -771,16 +771,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="374.4" x14ac:dyDescent="0.3">
@@ -788,35 +788,35 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/detail/detail.xlsx
+++ b/detail/detail.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectSkripsi\Skripsi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectSkripsi\trainModel\websites\detail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1410B809-0F73-4418-9863-37497AB691F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B350B72-A0EC-4303-85E8-0E509550C3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D421E984-B7D9-42C2-B457-45490D1096D1}"/>
   </bookViews>
@@ -60,9 +60,6 @@
     <t>Topeng Wijil</t>
   </si>
   <si>
-    <t>Topneg Keras</t>
-  </si>
-  <si>
     <t>Topeng Bujuh</t>
   </si>
   <si>
@@ -319,6 +316,9 @@
   </si>
   <si>
     <t>Topeng Bondres</t>
+  </si>
+  <si>
+    <t>Topeng Keras</t>
   </si>
 </sst>
 </file>
@@ -693,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -701,13 +701,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -715,13 +715,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -729,13 +729,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="360" x14ac:dyDescent="0.3">
@@ -743,13 +743,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -757,66 +757,66 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
